--- a/data/trans_bre/P1416-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1416-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>68,1%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 7,29</t>
+          <t>-1,65; 7,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 9,04</t>
+          <t>0,64; 8,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 8,03</t>
+          <t>0,34; 8,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 10,3</t>
+          <t>1,98; 9,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 126,34</t>
+          <t>-18,99; 123,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,9; 213,84</t>
+          <t>7,63; 209,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 180,76</t>
+          <t>3,47; 183,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,74; 141,24</t>
+          <t>17,74; 140,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 11,3</t>
+          <t>1,76; 11,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,17</t>
+          <t>1,19; 9,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,61</t>
+          <t>0,88; 9,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 6,7</t>
+          <t>-0,48; 7,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,57; 214,75</t>
+          <t>16,34; 197,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,91; 265,48</t>
+          <t>9,11; 249,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 216,88</t>
+          <t>6,68; 242,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 82,52</t>
+          <t>-4,63; 92,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,35</t>
+          <t>-5,32; 3,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,75</t>
+          <t>-1,62; 6,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 12,49</t>
+          <t>2,19; 12,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 14,46</t>
+          <t>-3,17; 7,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,51; 54,13</t>
+          <t>-61,06; 49,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 126,36</t>
+          <t>-25,81; 147,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,26; 334,63</t>
+          <t>30,93; 351,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 387,35</t>
+          <t>-21,98; 68,49</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,76</t>
+          <t>1,68; 6,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,74</t>
+          <t>1,61; 6,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,76</t>
+          <t>2,18; 6,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 4,57</t>
+          <t>1,63; 6,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,39; 132,45</t>
+          <t>22,64; 127,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,31; 174,63</t>
+          <t>29,45; 188,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,15; 238,43</t>
+          <t>46,62; 223,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,87; 63,49</t>
+          <t>17,12; 103,99</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-14,13%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,58</t>
+          <t>1,39; 8,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,19</t>
+          <t>-1,83; 2,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,22</t>
+          <t>0,06; 5,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 2,16</t>
+          <t>-2,37; 4,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,98; 226,02</t>
+          <t>17,09; 241,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 131,2</t>
+          <t>-35,38; 103,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 155,94</t>
+          <t>0,01; 159,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 24,47</t>
+          <t>-18,21; 63,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-8,09</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-49,82%</t>
+          <t>-43,72%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,5</t>
+          <t>-3,7; 3,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,36</t>
+          <t>-5,3; 2,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 0,23</t>
+          <t>-7,6; 0,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,9; -0,69</t>
+          <t>-15,06; 0,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 66,89</t>
+          <t>-35,28; 62,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 51,8</t>
+          <t>-48,12; 47,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,97; 5,53</t>
+          <t>-56,39; 4,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,92; -6,58</t>
+          <t>-67,28; 6,8</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,18</t>
+          <t>1,57; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,38</t>
+          <t>0,98; 3,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,11</t>
+          <t>1,74; 4,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,45</t>
+          <t>0,42; 3,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,32; 68,75</t>
+          <t>20,92; 72,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,59; 75,12</t>
+          <t>16,99; 75,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,18; 93,91</t>
+          <t>31,81; 95,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 42,86</t>
+          <t>3,76; 39,19</t>
         </is>
       </c>
     </row>
